--- a/analysis/model-valenos.xlsx
+++ b/analysis/model-valenos.xlsx
@@ -14,6 +14,7 @@
     <sheet name="Plan 12 miesiecy" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Kohorta founding" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Wykorzystanie srodkow" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Model cenowy" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -501,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1251,6 +1252,141 @@
       <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Zalozenie</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>Scenariusze wolumenu agenta na klienta (miesiecznie)</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="n"/>
+      <c r="C71" s="6" t="n"/>
+      <c r="D71" s="6" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>Pozycja</t>
+        </is>
+      </c>
+      <c r="B72" s="10" t="inlineStr">
+        <is>
+          <t>Niski</t>
+        </is>
+      </c>
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t>Sredni</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>Wysoki</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>Firmy przeskanowane</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="C73" s="8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D73" s="8" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>Firmy wzbogacone</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="C74" s="8" t="n">
+        <v>250</v>
+      </c>
+      <c r="D74" s="8" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>Kontakty wzbogacone</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C75" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="D75" s="8" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>Maile wyslane</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="n">
+        <v>600</v>
+      </c>
+      <c r="C76" s="8" t="n">
+        <v>2400</v>
+      </c>
+      <c r="D76" s="8" t="n">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>Akcje agenta CRM</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="n">
+        <v>400</v>
+      </c>
+      <c r="C77" s="8" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D77" s="8" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>Dane na klienta (PLN)</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="C78" s="8" t="n">
+        <v>240</v>
+      </c>
+      <c r="D78" s="8" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Scenariusze sa ZALOZENIEM. Zmierz je na czterech firmach testujacych i wpisz prawdziwe liczby.</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -1277,7 +1413,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Koszt obslugi jednego klienta miesiecznie (PLN)</t>
+          <t>Koszt obslugi: gotowka a koszt pelny</t>
         </is>
       </c>
     </row>
@@ -1401,15 +1537,26 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Inferencja nie spada ze skala: ta sama kwota przy 1 i przy 50 klientach. To jedyny koszt, ktory zostaje.</t>
+          <t>UWAGA: wiersz Razem to koszt PELNY, czyli z infrastruktura platformy podzielona przez liczbe klientow i z wycenionym czasem zalozycieli.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Przy braku optymalizacji ekstrakcji tresci (0,60 USD za firme zamiast 0,15) inferencja rosnie ok. 2,4x - zmien B7 w Zalozeniach i zobacz skutek.</t>
-        </is>
+          <t>Gotowka wychodzaca to tylko inferencja plus dane. Przy jednym kliencie infrastruktura to cala platforma, a nie koszt tego klienta. Patrz zakladka Model cenowy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Koszt krancowy gotowkowy na klienta (sredni wolumen)</t>
+        </is>
+      </c>
+      <c r="B12" s="26">
+        <f>B4+B5</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -3481,4 +3628,313 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Model cenowy: co naprawde kosztuje obsluga klienta</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Tylko gotowka wychodzaca. Infrastruktura platformy i czas zalozycieli NIE sa kosztem na klienta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Skladnik</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Niski wolumen</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Sredni wolumen</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Wysoki wolumen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Inferencja modelowa</t>
+        </is>
+      </c>
+      <c r="B5" s="16">
+        <f>('Zalozenia'!$B$6*'Zalozenia'!$B$73+'Zalozenia'!$B$7*'Zalozenia'!$B$74+'Zalozenia'!$B$8*'Zalozenia'!$B$75+'Zalozenia'!$B$9*'Zalozenia'!$B$76+'Zalozenia'!$B$10*'Zalozenia'!$B$77)*'Zalozenia'!$B$3</f>
+        <v/>
+      </c>
+      <c r="C5" s="16">
+        <f>('Zalozenia'!$B$6*'Zalozenia'!$C$73+'Zalozenia'!$B$7*'Zalozenia'!$C$74+'Zalozenia'!$B$8*'Zalozenia'!$C$75+'Zalozenia'!$B$9*'Zalozenia'!$C$76+'Zalozenia'!$B$10*'Zalozenia'!$C$77)*'Zalozenia'!$B$3</f>
+        <v/>
+      </c>
+      <c r="D5" s="16">
+        <f>('Zalozenia'!$B$6*'Zalozenia'!$D$73+'Zalozenia'!$B$7*'Zalozenia'!$D$74+'Zalozenia'!$B$8*'Zalozenia'!$D$75+'Zalozenia'!$B$9*'Zalozenia'!$D$76+'Zalozenia'!$B$10*'Zalozenia'!$D$77)*'Zalozenia'!$B$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Dane: Apollo, wyszukiwarka, weryfikacja</t>
+        </is>
+      </c>
+      <c r="B6" s="16">
+        <f>'Zalozenia'!$B$78</f>
+        <v/>
+      </c>
+      <c r="C6" s="16">
+        <f>'Zalozenia'!$C$78</f>
+        <v/>
+      </c>
+      <c r="D6" s="16">
+        <f>'Zalozenia'!$D$78</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Koszt krancowy gotowkowy na klienta</t>
+        </is>
+      </c>
+      <c r="B7" s="15">
+        <f>B5+B6</f>
+        <v/>
+      </c>
+      <c r="C7" s="15">
+        <f>C5+C6</f>
+        <v/>
+      </c>
+      <c r="D7" s="15">
+        <f>D5+D6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Rozpietosc miedzy najlzejszym a najciezszym klientem</t>
+        </is>
+      </c>
+      <c r="B9" s="29">
+        <f>D7/B7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Limit stanowisk NIE ogranicza tej rozpietosci. Ten sam klient moze miec 3 stanowiska przy kazdym z tych wolumenow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Koszt krancowy jako udzial ceny</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Cena abonamentu</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Niski</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Sredni</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Wysoki</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16">
+        <f>'Zalozenia'!$B$31</f>
+        <v/>
+      </c>
+      <c r="B15" s="17">
+        <f>B$7/$A15</f>
+        <v/>
+      </c>
+      <c r="C15" s="17">
+        <f>C$7/$A15</f>
+        <v/>
+      </c>
+      <c r="D15" s="17">
+        <f>D$7/$A15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16">
+        <f>'Zalozenia'!$B$32</f>
+        <v/>
+      </c>
+      <c r="B16" s="17">
+        <f>B$7/$A16</f>
+        <v/>
+      </c>
+      <c r="C16" s="17">
+        <f>C$7/$A16</f>
+        <v/>
+      </c>
+      <c r="D16" s="17">
+        <f>D$7/$A16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Rama porownawcza dla kupujacego (PLN/mies., szacunki rynkowe)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Alternatywa klienta</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Od</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Do</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Junior SDR, pelny koszt pracodawcy</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="n">
+        <v>8500</v>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Agencja outboundowa, retainer</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>CRM rozliczany per stanowisko, 5 stanowisk</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="n">
+        <v>245</v>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>ValenOS przy cenie standard</t>
+        </is>
+      </c>
+      <c r="B25" s="26">
+        <f>'Zalozenia'!$B$32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Przy wycenie per stanowisko, 5 stanowisk, wyszloby na stanowisko</t>
+        </is>
+      </c>
+      <c r="B26" s="16">
+        <f>'Zalozenia'!$B$32/5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Gorna granica polskiego rynku CRM za stanowisko</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ile razy powyzej rynku</t>
+        </is>
+      </c>
+      <c r="B28" s="29">
+        <f>B26/B27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Wniosek: retainer ustawia porownanie z kosztem handlowca lub agencji, gdzie ValenOS wygrywa. Wycena per stanowisko ustawia porownanie z Pipedrive, gdzie przegrywa 4x.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/analysis/model-valenos.xlsx
+++ b/analysis/model-valenos.xlsx
@@ -9,12 +9,13 @@
   <sheets>
     <sheet name="Zalozenia" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Koszt obslugi" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Marza CAC LTV" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Prog rentownosci" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Plan 12 miesiecy" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Cennik" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Marza CAC LTV" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Prog rentownosci" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Kohorta founding" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Wykorzystanie srodkow" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Model cenowy" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Plan 12 miesiecy" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -101,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -137,6 +138,10 @@
     <xf numFmtId="167" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -502,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D79"/>
+  <dimension ref="A1:D98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1387,6 +1392,106 @@
       <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Scenariusze sa ZALOZENIEM. Zmierz je na czterech firmach testujacych i wpisz prawdziwe liczby.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>Plan masowy: konwersja i przepustowosc</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="n"/>
+      <c r="C92" s="6" t="n"/>
+      <c r="D92" s="6" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>Konwersja ze spotkania, mies. 1-3</t>
+        </is>
+      </c>
+      <c r="B93" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>ZALOZENIE. Nizsza cena powinna dac wyzsza konwersje niz 6% przy 5 000 PLN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>Konwersja, mies. 4-6</t>
+        </is>
+      </c>
+      <c r="B94" s="13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Zalozenie</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>Konwersja, mies. 7-9</t>
+        </is>
+      </c>
+      <c r="B95" s="13" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Zalozenie</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>Konwersja, mies. 10-12</t>
+        </is>
+      </c>
+      <c r="B96" s="13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Zalozenie</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>Onboarding na klienta (h)</t>
+        </is>
+      </c>
+      <c r="B97" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Model masowy. W modelu bespoke bylo 8 h.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>Wsparcie na klienta (h/mies.)</t>
+        </is>
+      </c>
+      <c r="B98" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Model masowy. W modelu bespoke bylo 3 h.</t>
         </is>
       </c>
     </row>
@@ -1573,6 +1678,419 @@
   <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Cennik: retainer z limitem stanowisk i pakietem wolumenu</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Niebieskie komorki to dane wejsciowe. Pakiety wolumenu ustaw na podstawie pomiaru na czterech firmach testujacych.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Pozycja</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Skala</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Stanowiska w cenie</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Firmy przeskanowane / mies.</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>800</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Firmy wzbogacone / mies.</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>200</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Kontakty wzbogacone / mies.</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>500</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Maile / mies.</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n">
+        <v>500</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Akcje agenta CRM / mies.</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>500</v>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Dane na klienta (PLN/mies.)</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>180</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Cena (PLN/mies.)</t>
+        </is>
+      </c>
+      <c r="B13" s="34" t="n">
+        <v>990</v>
+      </c>
+      <c r="C13" s="34" t="n">
+        <v>2490</v>
+      </c>
+      <c r="D13" s="34" t="n">
+        <v>5900</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Inferencja</t>
+        </is>
+      </c>
+      <c r="B15" s="16">
+        <f>('Zalozenia'!$B$6*B6+'Zalozenia'!$B$7*B7+'Zalozenia'!$B$8*B8+'Zalozenia'!$B$9*B9+'Zalozenia'!$B$10*B10)*'Zalozenia'!$B$3</f>
+        <v/>
+      </c>
+      <c r="C15" s="16">
+        <f>('Zalozenia'!$B$6*C6+'Zalozenia'!$B$7*C7+'Zalozenia'!$B$8*C8+'Zalozenia'!$B$9*C9+'Zalozenia'!$B$10*C10)*'Zalozenia'!$B$3</f>
+        <v/>
+      </c>
+      <c r="D15" s="16">
+        <f>('Zalozenia'!$B$6*D6+'Zalozenia'!$B$7*D7+'Zalozenia'!$B$8*D8+'Zalozenia'!$B$9*D9+'Zalozenia'!$B$10*D10)*'Zalozenia'!$B$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Dane</t>
+        </is>
+      </c>
+      <c r="B16" s="16">
+        <f>B11</f>
+        <v/>
+      </c>
+      <c r="C16" s="16">
+        <f>C11</f>
+        <v/>
+      </c>
+      <c r="D16" s="16">
+        <f>D11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Koszt krancowy gotowkowy</t>
+        </is>
+      </c>
+      <c r="B17" s="26">
+        <f>B15+B16</f>
+        <v/>
+      </c>
+      <c r="C17" s="26">
+        <f>C15+C16</f>
+        <v/>
+      </c>
+      <c r="D17" s="26">
+        <f>D15+D16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Zysk brutto</t>
+        </is>
+      </c>
+      <c r="B18" s="26">
+        <f>B13-B17</f>
+        <v/>
+      </c>
+      <c r="C18" s="26">
+        <f>C13-C17</f>
+        <v/>
+      </c>
+      <c r="D18" s="26">
+        <f>D13-D17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Marza brutto</t>
+        </is>
+      </c>
+      <c r="B19" s="30">
+        <f>B18/B13</f>
+        <v/>
+      </c>
+      <c r="C19" s="30">
+        <f>C18/C13</f>
+        <v/>
+      </c>
+      <c r="D19" s="30">
+        <f>D18/D13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>Mieszanka klientow</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Udzial</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Cena</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Koszt</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C23" s="16">
+        <f>B13</f>
+        <v/>
+      </c>
+      <c r="D23" s="16">
+        <f>B17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="C24" s="16">
+        <f>C13</f>
+        <v/>
+      </c>
+      <c r="D24" s="16">
+        <f>C17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Skala</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C25" s="16">
+        <f>D13</f>
+        <v/>
+      </c>
+      <c r="D25" s="16">
+        <f>D17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Srednia wazona cena</t>
+        </is>
+      </c>
+      <c r="B26" s="26">
+        <f>SUMPRODUCT(B23:B25,C23:C25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>Sredni wazony koszt</t>
+        </is>
+      </c>
+      <c r="B27" s="26">
+        <f>SUMPRODUCT(B23:B25,D23:D25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Sredni zysk brutto</t>
+        </is>
+      </c>
+      <c r="B28" s="26">
+        <f>B26-B27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Srednia marza</t>
+        </is>
+      </c>
+      <c r="B29" s="31">
+        <f>B28/B26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Bez oplaty wdrozeniowej. Caly przychod jest powtarzalny.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
@@ -1907,7 +2425,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1965,7 +2483,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Bez wynagrodzen, cena founding</t>
+          <t>Bez wynagrodzen</t>
         </is>
       </c>
       <c r="B6" s="16">
@@ -1973,7 +2491,7 @@
         <v/>
       </c>
       <c r="C6" s="16">
-        <f>'Marza CAC LTV'!C4</f>
+        <f>Cennik!$B$28</f>
         <v/>
       </c>
       <c r="D6" s="10">
@@ -1984,15 +2502,15 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Bez wynagrodzen, cena standard</t>
+          <t>Pensja dla Bruna</t>
         </is>
       </c>
       <c r="B7" s="16">
-        <f>B3</f>
+        <f>B3+'Zalozenia'!$B$47</f>
         <v/>
       </c>
       <c r="C7" s="16">
-        <f>'Marza CAC LTV'!C6</f>
+        <f>Cennik!$B$28</f>
         <v/>
       </c>
       <c r="D7" s="10">
@@ -2003,15 +2521,15 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Pensja dla Bruna, cena standard</t>
+          <t>Pensje dla obu zalozycieli</t>
         </is>
       </c>
       <c r="B8" s="16">
-        <f>B3+'Zalozenia'!$B$47</f>
+        <f>B3+'Zalozenia'!$B$48</f>
         <v/>
       </c>
       <c r="C8" s="16">
-        <f>'Marza CAC LTV'!C6</f>
+        <f>Cennik!$B$28</f>
         <v/>
       </c>
       <c r="D8" s="10">
@@ -2020,1162 +2538,51 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Pensje dla obu, cena standard</t>
-        </is>
-      </c>
-      <c r="B9" s="16">
-        <f>B3+'Zalozenia'!$B$48</f>
-        <v/>
-      </c>
-      <c r="C9" s="16">
-        <f>'Marza CAC LTV'!C6</f>
-        <v/>
-      </c>
-      <c r="D9" s="10">
-        <f>ROUNDUP(B9/C9,0)</f>
-        <v/>
-      </c>
+      <c r="A9" s="3" t="n"/>
+      <c r="B9" s="16" t="n"/>
+      <c r="C9" s="16" t="n"/>
+      <c r="D9" s="10" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>Mieszanka realna: 4 founding + reszta standard, pensje dla obu</t>
-        </is>
-      </c>
-      <c r="B11" s="16">
-        <f>B3+'Zalozenia'!$B$48</f>
-        <v/>
-      </c>
+          <t>Sufit przepustowosci, model masowy</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pokrycie z 4 klientow founding</t>
-        </is>
-      </c>
-      <c r="B12" s="16">
-        <f>'Zalozenia'!$B$63*'Marza CAC LTV'!C4</f>
+          <t>Godziny Mario przy 50 klientach</t>
+        </is>
+      </c>
+      <c r="B12" s="35">
+        <f>40+'Zalozenia'!$B$51*1.5+5*'Zalozenia'!$B$97+50*'Zalozenia'!$B$98</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Potrzebni klienci standard</t>
-        </is>
-      </c>
-      <c r="B13" s="10">
-        <f>ROUNDUP((B11-B12)/'Marza CAC LTV'!C6,0)</f>
+          <t>Godziny Mario przy 100 klientach</t>
+        </is>
+      </c>
+      <c r="B13" s="36">
+        <f>40+'Zalozenia'!$B$51*1.5+5*'Zalozenia'!$B$97+100*'Zalozenia'!$B$98</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>Razem klientow</t>
-        </is>
-      </c>
-      <c r="B14" s="10">
-        <f>'Zalozenia'!$B$63+B13</f>
-        <v/>
-      </c>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>W modelu bespoke sufit wypadal okolo 20 klientow.</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Sufit przepustowosci: przy 3 h wsparcia na klienta Mario wysyca sie okolo 20 klientow. Pierwsza osoba do wdrozen jest potrzebna przy 15-18.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:S19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Plan dwunastu miesiecy od startu produktu</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>PROGNOZA. Kazda liczba wynika z zakladki Zalozenia.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="24" t="inlineStr">
-        <is>
-          <t>Mies.</t>
-        </is>
-      </c>
-      <c r="B4" s="24" t="inlineStr">
-        <is>
-          <t>Konwersja</t>
-        </is>
-      </c>
-      <c r="C4" s="24" t="inlineStr">
-        <is>
-          <t>Zamkniec</t>
-        </is>
-      </c>
-      <c r="D4" s="24" t="inlineStr">
-        <is>
-          <t>Founding po churnie</t>
-        </is>
-      </c>
-      <c r="E4" s="24" t="inlineStr">
-        <is>
-          <t>Founding nowi</t>
-        </is>
-      </c>
-      <c r="F4" s="24" t="inlineStr">
-        <is>
-          <t>Founding razem</t>
-        </is>
-      </c>
-      <c r="G4" s="24" t="inlineStr">
-        <is>
-          <t>Standard po churnie</t>
-        </is>
-      </c>
-      <c r="H4" s="24" t="inlineStr">
-        <is>
-          <t>Standard nowi</t>
-        </is>
-      </c>
-      <c r="I4" s="24" t="inlineStr">
-        <is>
-          <t>Standard razem</t>
-        </is>
-      </c>
-      <c r="J4" s="24" t="inlineStr">
-        <is>
-          <t>Klientow razem</t>
-        </is>
-      </c>
-      <c r="K4" s="24" t="inlineStr">
-        <is>
-          <t>MRR</t>
-        </is>
-      </c>
-      <c r="L4" s="24" t="inlineStr">
-        <is>
-          <t>Wdrozeniowe</t>
-        </is>
-      </c>
-      <c r="M4" s="24" t="inlineStr">
-        <is>
-          <t>Przychod</t>
-        </is>
-      </c>
-      <c r="N4" s="24" t="inlineStr">
-        <is>
-          <t>Koszt/klienta</t>
-        </is>
-      </c>
-      <c r="O4" s="24" t="inlineStr">
-        <is>
-          <t>COGS</t>
-        </is>
-      </c>
-      <c r="P4" s="24" t="inlineStr">
-        <is>
-          <t>Koszty stale</t>
-        </is>
-      </c>
-      <c r="Q4" s="24" t="inlineStr">
-        <is>
-          <t>Osoba</t>
-        </is>
-      </c>
-      <c r="R4" s="24" t="inlineStr">
-        <is>
-          <t>Wynik</t>
-        </is>
-      </c>
-      <c r="S4" s="24" t="inlineStr">
-        <is>
-          <t>Narastajaco</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="17">
-        <f>IF(A5&lt;=3,'Zalozenia'!$B$58,IF(A5&lt;=6,'Zalozenia'!$B$59,IF(A5&lt;=9,'Zalozenia'!$B$60,'Zalozenia'!$B$61)))</f>
-        <v/>
-      </c>
-      <c r="C5" s="25">
-        <f>'Zalozenia'!$B$51*B5</f>
-        <v/>
-      </c>
-      <c r="D5" s="25">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="E5" s="25">
-        <f>IF(A5&lt;=3,MIN(C5,MAX(0,'Zalozenia'!$B$63-D5)),0)</f>
-        <v/>
-      </c>
-      <c r="F5" s="25">
-        <f>D5+E5</f>
-        <v/>
-      </c>
-      <c r="G5" s="25">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="H5" s="25">
-        <f>C5-E5</f>
-        <v/>
-      </c>
-      <c r="I5" s="25">
-        <f>G5+H5</f>
-        <v/>
-      </c>
-      <c r="J5" s="25">
-        <f>F5+I5</f>
-        <v/>
-      </c>
-      <c r="K5" s="16">
-        <f>F5*'Zalozenia'!$B$31+I5*'Zalozenia'!$B$32</f>
-        <v/>
-      </c>
-      <c r="L5" s="16">
-        <f>H5*'Zalozenia'!$B$33</f>
-        <v/>
-      </c>
-      <c r="M5" s="16">
-        <f>K5+L5</f>
-        <v/>
-      </c>
-      <c r="N5" s="16">
-        <f>IF(A5&lt;=3,'Zalozenia'!$B$64,IF(A5&lt;=8,'Zalozenia'!$B$65,'Zalozenia'!$B$66))</f>
-        <v/>
-      </c>
-      <c r="O5" s="16">
-        <f>J5*N5</f>
-        <v/>
-      </c>
-      <c r="P5" s="16">
-        <f>'Zalozenia'!$B$41+'Zalozenia'!$B$42</f>
-        <v/>
-      </c>
-      <c r="Q5" s="16">
-        <f>IF(A5&gt;='Zalozenia'!$B$67,'Zalozenia'!$B$68,0)</f>
-        <v/>
-      </c>
-      <c r="R5" s="16">
-        <f>M5-O5-P5-Q5</f>
-        <v/>
-      </c>
-      <c r="S5" s="16">
-        <f>R5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="17">
-        <f>IF(A6&lt;=3,'Zalozenia'!$B$58,IF(A6&lt;=6,'Zalozenia'!$B$59,IF(A6&lt;=9,'Zalozenia'!$B$60,'Zalozenia'!$B$61)))</f>
-        <v/>
-      </c>
-      <c r="C6" s="25">
-        <f>'Zalozenia'!$B$51*B6</f>
-        <v/>
-      </c>
-      <c r="D6" s="25">
-        <f>F5*(1-'Zalozenia'!$B$62)</f>
-        <v/>
-      </c>
-      <c r="E6" s="25">
-        <f>IF(A6&lt;=3,MIN(C6,MAX(0,'Zalozenia'!$B$63-D6)),0)</f>
-        <v/>
-      </c>
-      <c r="F6" s="25">
-        <f>D6+E6</f>
-        <v/>
-      </c>
-      <c r="G6" s="25">
-        <f>I5*(1-'Zalozenia'!$B$62)</f>
-        <v/>
-      </c>
-      <c r="H6" s="25">
-        <f>C6-E6</f>
-        <v/>
-      </c>
-      <c r="I6" s="25">
-        <f>G6+H6</f>
-        <v/>
-      </c>
-      <c r="J6" s="25">
-        <f>F6+I6</f>
-        <v/>
-      </c>
-      <c r="K6" s="16">
-        <f>F6*'Zalozenia'!$B$31+I6*'Zalozenia'!$B$32</f>
-        <v/>
-      </c>
-      <c r="L6" s="16">
-        <f>H6*'Zalozenia'!$B$33</f>
-        <v/>
-      </c>
-      <c r="M6" s="16">
-        <f>K6+L6</f>
-        <v/>
-      </c>
-      <c r="N6" s="16">
-        <f>IF(A6&lt;=3,'Zalozenia'!$B$64,IF(A6&lt;=8,'Zalozenia'!$B$65,'Zalozenia'!$B$66))</f>
-        <v/>
-      </c>
-      <c r="O6" s="16">
-        <f>J6*N6</f>
-        <v/>
-      </c>
-      <c r="P6" s="16">
-        <f>'Zalozenia'!$B$41+'Zalozenia'!$B$42</f>
-        <v/>
-      </c>
-      <c r="Q6" s="16">
-        <f>IF(A6&gt;='Zalozenia'!$B$67,'Zalozenia'!$B$68,0)</f>
-        <v/>
-      </c>
-      <c r="R6" s="16">
-        <f>M6-O6-P6-Q6</f>
-        <v/>
-      </c>
-      <c r="S6" s="16">
-        <f>S5+R6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="17">
-        <f>IF(A7&lt;=3,'Zalozenia'!$B$58,IF(A7&lt;=6,'Zalozenia'!$B$59,IF(A7&lt;=9,'Zalozenia'!$B$60,'Zalozenia'!$B$61)))</f>
-        <v/>
-      </c>
-      <c r="C7" s="25">
-        <f>'Zalozenia'!$B$51*B7</f>
-        <v/>
-      </c>
-      <c r="D7" s="25">
-        <f>F6*(1-'Zalozenia'!$B$62)</f>
-        <v/>
-      </c>
-      <c r="E7" s="25">
-        <f>IF(A7&lt;=3,MIN(C7,MAX(0,'Zalozenia'!$B$63-D7)),0)</f>
-        <v/>
-      </c>
-      <c r="F7" s="25">
-        <f>D7+E7</f>
-        <v/>
-      </c>
-      <c r="G7" s="25">
-        <f>I6*(1-'Zalozenia'!$B$62)</f>
-        <v/>
-      </c>
-      <c r="H7" s="25">
-        <f>C7-E7</f>
-        <v/>
-      </c>
-      <c r="I7" s="25">
-        <f>G7+H7</f>
-        <v/>
-      </c>
-      <c r="J7" s="25">
-        <f>F7+I7</f>
-        <v/>
-      </c>
-      <c r="K7" s="16">
-        <f>F7*'Zalozenia'!$B$31+I7*'Zalozenia'!$B$32</f>
-        <v/>
-      </c>
-      <c r="L7" s="16">
-        <f>H7*'Zalozenia'!$B$33</f>
-        <v/>
-      </c>
-      <c r="M7" s="16">
-        <f>K7+L7</f>
-        <v/>
-      </c>
-      <c r="N7" s="16">
-        <f>IF(A7&lt;=3,'Zalozenia'!$B$64,IF(A7&lt;=8,'Zalozenia'!$B$65,'Zalozenia'!$B$66))</f>
-        <v/>
-      </c>
-      <c r="O7" s="16">
-        <f>J7*N7</f>
-        <v/>
-      </c>
-      <c r="P7" s="16">
-        <f>'Zalozenia'!$B$41+'Zalozenia'!$B$42</f>
-        <v/>
-      </c>
-      <c r="Q7" s="16">
-        <f>IF(A7&gt;='Zalozenia'!$B$67,'Zalozenia'!$B$68,0)</f>
-        <v/>
-      </c>
-      <c r="R7" s="16">
-        <f>M7-O7-P7-Q7</f>
-        <v/>
-      </c>
-      <c r="S7" s="16">
-        <f>S6+R7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="17">
-        <f>IF(A8&lt;=3,'Zalozenia'!$B$58,IF(A8&lt;=6,'Zalozenia'!$B$59,IF(A8&lt;=9,'Zalozenia'!$B$60,'Zalozenia'!$B$61)))</f>
-        <v/>
-      </c>
-      <c r="C8" s="25">
-        <f>'Zalozenia'!$B$51*B8</f>
-        <v/>
-      </c>
-      <c r="D8" s="25">
-        <f>F7*(1-'Zalozenia'!$B$62)</f>
-        <v/>
-      </c>
-      <c r="E8" s="25">
-        <f>IF(A8&lt;=3,MIN(C8,MAX(0,'Zalozenia'!$B$63-D8)),0)</f>
-        <v/>
-      </c>
-      <c r="F8" s="25">
-        <f>D8+E8</f>
-        <v/>
-      </c>
-      <c r="G8" s="25">
-        <f>I7*(1-'Zalozenia'!$B$62)</f>
-        <v/>
-      </c>
-      <c r="H8" s="25">
-        <f>C8-E8</f>
-        <v/>
-      </c>
-      <c r="I8" s="25">
-        <f>G8+H8</f>
-        <v/>
-      </c>
-      <c r="J8" s="25">
-        <f>F8+I8</f>
-        <v/>
-      </c>
-      <c r="K8" s="16">
-        <f>F8*'Zalozenia'!$B$31+I8*'Zalozenia'!$B$32</f>
-        <v/>
-      </c>
-      <c r="L8" s="16">
-        <f>H8*'Zalozenia'!$B$33</f>
-        <v/>
-      </c>
-      <c r="M8" s="16">
-        <f>K8+L8</f>
-        <v/>
-      </c>
-      <c r="N8" s="16">
-        <f>IF(A8&lt;=3,'Zalozenia'!$B$64,IF(A8&lt;=8,'Zalozenia'!$B$65,'Zalozenia'!$B$66))</f>
-        <v/>
-      </c>
-      <c r="O8" s="16">
-        <f>J8*N8</f>
-        <v/>
-      </c>
-      <c r="P8" s="16">
-        <f>'Zalozenia'!$B$41+'Zalozenia'!$B$42</f>
-        <v/>
-      </c>
-      <c r="Q8" s="16">
-        <f>IF(A8&gt;='Zalozenia'!$B$67,'Zalozenia'!$B$68,0)</f>
-        <v/>
-      </c>
-      <c r="R8" s="16">
-        <f>M8-O8-P8-Q8</f>
-        <v/>
-      </c>
-      <c r="S8" s="16">
-        <f>S7+R8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="17">
-        <f>IF(A9&lt;=3,'Zalozenia'!$B$58,IF(A9&lt;=6,'Zalozenia'!$B$59,IF(A9&lt;=9,'Zalozenia'!$B$60,'Zalozenia'!$B$61)))</f>
-        <v/>
-      </c>
-      <c r="C9" s="25">
-        <f>'Zalozenia'!$B$51*B9</f>
-        <v/>
-      </c>
-      <c r="D9" s="25">
-        <f>F8*(1-'Zalozenia'!$B$62)</f>
-        <v/>
-      </c>
-      <c r="E9" s="25">
-        <f>IF(A9&lt;=3,MIN(C9,MAX(0,'Zalozenia'!$B$63-D9)),0)</f>
-        <v/>
-      </c>
-      <c r="F9" s="25">
-        <f>D9+E9</f>
-        <v/>
-      </c>
-      <c r="G9" s="25">
-        <f>I8*(1-'Zalozenia'!$B$62)</f>
-        <v/>
-      </c>
-      <c r="H9" s="25">
-        <f>C9-E9</f>
-        <v/>
-      </c>
-      <c r="I9" s="25">
-        <f>G9+H9</f>
-        <v/>
-      </c>
-      <c r="J9" s="25">
-        <f>F9+I9</f>
-        <v/>
-      </c>
-      <c r="K9" s="16">
-        <f>F9*'Zalozenia'!$B$31+I9*'Zalozenia'!$B$32</f>
-        <v/>
-      </c>
-      <c r="L9" s="16">
-        <f>H9*'Zalozenia'!$B$33</f>
-        <v/>
-      </c>
-      <c r="M9" s="16">
-        <f>K9+L9</f>
-        <v/>
-      </c>
-      <c r="N9" s="16">
-        <f>IF(A9&lt;=3,'Zalozenia'!$B$64,IF(A9&lt;=8,'Zalozenia'!$B$65,'Zalozenia'!$B$66))</f>
-        <v/>
-      </c>
-      <c r="O9" s="16">
-        <f>J9*N9</f>
-        <v/>
-      </c>
-      <c r="P9" s="16">
-        <f>'Zalozenia'!$B$41+'Zalozenia'!$B$42</f>
-        <v/>
-      </c>
-      <c r="Q9" s="16">
-        <f>IF(A9&gt;='Zalozenia'!$B$67,'Zalozenia'!$B$68,0)</f>
-        <v/>
-      </c>
-      <c r="R9" s="16">
-        <f>M9-O9-P9-Q9</f>
-        <v/>
-      </c>
-      <c r="S9" s="16">
-        <f>S8+R9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="17">
-        <f>IF(A10&lt;=3,'Zalozenia'!$B$58,IF(A10&lt;=6,'Zalozenia'!$B$59,IF(A10&lt;=9,'Zalozenia'!$B$60,'Zalozenia'!$B$61)))</f>
-        <v/>
-      </c>
-      <c r="C10" s="25">
-        <f>'Zalozenia'!$B$51*B10</f>
-        <v/>
-      </c>
-      <c r="D10" s="25">
-        <f>F9*(1-'Zalozenia'!$B$62)</f>
-        <v/>
-      </c>
-      <c r="E10" s="25">
-        <f>IF(A10&lt;=3,MIN(C10,MAX(0,'Zalozenia'!$B$63-D10)),0)</f>
-        <v/>
-      </c>
-      <c r="F10" s="25">
-        <f>D10+E10</f>
-        <v/>
-      </c>
-      <c r="G10" s="25">
-        <f>I9*(1-'Zalozenia'!$B$62)</f>
-        <v/>
-      </c>
-      <c r="H10" s="25">
-        <f>C10-E10</f>
-        <v/>
-      </c>
-      <c r="I10" s="25">
-        <f>G10+H10</f>
-        <v/>
-      </c>
-      <c r="J10" s="25">
-        <f>F10+I10</f>
-        <v/>
-      </c>
-      <c r="K10" s="16">
-        <f>F10*'Zalozenia'!$B$31+I10*'Zalozenia'!$B$32</f>
-        <v/>
-      </c>
-      <c r="L10" s="16">
-        <f>H10*'Zalozenia'!$B$33</f>
-        <v/>
-      </c>
-      <c r="M10" s="16">
-        <f>K10+L10</f>
-        <v/>
-      </c>
-      <c r="N10" s="16">
-        <f>IF(A10&lt;=3,'Zalozenia'!$B$64,IF(A10&lt;=8,'Zalozenia'!$B$65,'Zalozenia'!$B$66))</f>
-        <v/>
-      </c>
-      <c r="O10" s="16">
-        <f>J10*N10</f>
-        <v/>
-      </c>
-      <c r="P10" s="16">
-        <f>'Zalozenia'!$B$41+'Zalozenia'!$B$42</f>
-        <v/>
-      </c>
-      <c r="Q10" s="16">
-        <f>IF(A10&gt;='Zalozenia'!$B$67,'Zalozenia'!$B$68,0)</f>
-        <v/>
-      </c>
-      <c r="R10" s="16">
-        <f>M10-O10-P10-Q10</f>
-        <v/>
-      </c>
-      <c r="S10" s="16">
-        <f>S9+R10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="17">
-        <f>IF(A11&lt;=3,'Zalozenia'!$B$58,IF(A11&lt;=6,'Zalozenia'!$B$59,IF(A11&lt;=9,'Zalozenia'!$B$60,'Zalozenia'!$B$61)))</f>
-        <v/>
-      </c>
-      <c r="C11" s="25">
-        <f>'Zalozenia'!$B$51*B11</f>
-        <v/>
-      </c>
-      <c r="D11" s="25">
-        <f>F10*(1-'Zalozenia'!$B$62)</f>
-        <v/>
-      </c>
-      <c r="E11" s="25">
-        <f>IF(A11&lt;=3,MIN(C11,MAX(0,'Zalozenia'!$B$63-D11)),0)</f>
-        <v/>
-      </c>
-      <c r="F11" s="25">
-        <f>D11+E11</f>
-        <v/>
-      </c>
-      <c r="G11" s="25">
-        <f>I10*(1-'Zalozenia'!$B$62)</f>
-        <v/>
-      </c>
-      <c r="H11" s="25">
-        <f>C11-E11</f>
-        <v/>
-      </c>
-      <c r="I11" s="25">
-        <f>G11+H11</f>
-        <v/>
-      </c>
-      <c r="J11" s="25">
-        <f>F11+I11</f>
-        <v/>
-      </c>
-      <c r="K11" s="16">
-        <f>F11*'Zalozenia'!$B$31+I11*'Zalozenia'!$B$32</f>
-        <v/>
-      </c>
-      <c r="L11" s="16">
-        <f>H11*'Zalozenia'!$B$33</f>
-        <v/>
-      </c>
-      <c r="M11" s="16">
-        <f>K11+L11</f>
-        <v/>
-      </c>
-      <c r="N11" s="16">
-        <f>IF(A11&lt;=3,'Zalozenia'!$B$64,IF(A11&lt;=8,'Zalozenia'!$B$65,'Zalozenia'!$B$66))</f>
-        <v/>
-      </c>
-      <c r="O11" s="16">
-        <f>J11*N11</f>
-        <v/>
-      </c>
-      <c r="P11" s="16">
-        <f>'Zalozenia'!$B$41+'Zalozenia'!$B$42</f>
-        <v/>
-      </c>
-      <c r="Q11" s="16">
-        <f>IF(A11&gt;='Zalozenia'!$B$67,'Zalozenia'!$B$68,0)</f>
-        <v/>
-      </c>
-      <c r="R11" s="16">
-        <f>M11-O11-P11-Q11</f>
-        <v/>
-      </c>
-      <c r="S11" s="16">
-        <f>S10+R11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="17">
-        <f>IF(A12&lt;=3,'Zalozenia'!$B$58,IF(A12&lt;=6,'Zalozenia'!$B$59,IF(A12&lt;=9,'Zalozenia'!$B$60,'Zalozenia'!$B$61)))</f>
-        <v/>
-      </c>
-      <c r="C12" s="25">
-        <f>'Zalozenia'!$B$51*B12</f>
-        <v/>
-      </c>
-      <c r="D12" s="25">
-        <f>F11*(1-'Zalozenia'!$B$62)</f>
-        <v/>
-      </c>
-      <c r="E12" s="25">
-        <f>IF(A12&lt;=3,MIN(C12,MAX(0,'Zalozenia'!$B$63-D12)),0)</f>
-        <v/>
-      </c>
-      <c r="F12" s="25">
-        <f>D12+E12</f>
-        <v/>
-      </c>
-      <c r="G12" s="25">
-        <f>I11*(1-'Zalozenia'!$B$62)</f>
-        <v/>
-      </c>
-      <c r="H12" s="25">
-        <f>C12-E12</f>
-        <v/>
-      </c>
-      <c r="I12" s="25">
-        <f>G12+H12</f>
-        <v/>
-      </c>
-      <c r="J12" s="25">
-        <f>F12+I12</f>
-        <v/>
-      </c>
-      <c r="K12" s="16">
-        <f>F12*'Zalozenia'!$B$31+I12*'Zalozenia'!$B$32</f>
-        <v/>
-      </c>
-      <c r="L12" s="16">
-        <f>H12*'Zalozenia'!$B$33</f>
-        <v/>
-      </c>
-      <c r="M12" s="16">
-        <f>K12+L12</f>
-        <v/>
-      </c>
-      <c r="N12" s="16">
-        <f>IF(A12&lt;=3,'Zalozenia'!$B$64,IF(A12&lt;=8,'Zalozenia'!$B$65,'Zalozenia'!$B$66))</f>
-        <v/>
-      </c>
-      <c r="O12" s="16">
-        <f>J12*N12</f>
-        <v/>
-      </c>
-      <c r="P12" s="16">
-        <f>'Zalozenia'!$B$41+'Zalozenia'!$B$42</f>
-        <v/>
-      </c>
-      <c r="Q12" s="16">
-        <f>IF(A12&gt;='Zalozenia'!$B$67,'Zalozenia'!$B$68,0)</f>
-        <v/>
-      </c>
-      <c r="R12" s="16">
-        <f>M12-O12-P12-Q12</f>
-        <v/>
-      </c>
-      <c r="S12" s="16">
-        <f>S11+R12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="17">
-        <f>IF(A13&lt;=3,'Zalozenia'!$B$58,IF(A13&lt;=6,'Zalozenia'!$B$59,IF(A13&lt;=9,'Zalozenia'!$B$60,'Zalozenia'!$B$61)))</f>
-        <v/>
-      </c>
-      <c r="C13" s="25">
-        <f>'Zalozenia'!$B$51*B13</f>
-        <v/>
-      </c>
-      <c r="D13" s="25">
-        <f>F12*(1-'Zalozenia'!$B$62)</f>
-        <v/>
-      </c>
-      <c r="E13" s="25">
-        <f>IF(A13&lt;=3,MIN(C13,MAX(0,'Zalozenia'!$B$63-D13)),0)</f>
-        <v/>
-      </c>
-      <c r="F13" s="25">
-        <f>D13+E13</f>
-        <v/>
-      </c>
-      <c r="G13" s="25">
-        <f>I12*(1-'Zalozenia'!$B$62)</f>
-        <v/>
-      </c>
-      <c r="H13" s="25">
-        <f>C13-E13</f>
-        <v/>
-      </c>
-      <c r="I13" s="25">
-        <f>G13+H13</f>
-        <v/>
-      </c>
-      <c r="J13" s="25">
-        <f>F13+I13</f>
-        <v/>
-      </c>
-      <c r="K13" s="16">
-        <f>F13*'Zalozenia'!$B$31+I13*'Zalozenia'!$B$32</f>
-        <v/>
-      </c>
-      <c r="L13" s="16">
-        <f>H13*'Zalozenia'!$B$33</f>
-        <v/>
-      </c>
-      <c r="M13" s="16">
-        <f>K13+L13</f>
-        <v/>
-      </c>
-      <c r="N13" s="16">
-        <f>IF(A13&lt;=3,'Zalozenia'!$B$64,IF(A13&lt;=8,'Zalozenia'!$B$65,'Zalozenia'!$B$66))</f>
-        <v/>
-      </c>
-      <c r="O13" s="16">
-        <f>J13*N13</f>
-        <v/>
-      </c>
-      <c r="P13" s="16">
-        <f>'Zalozenia'!$B$41+'Zalozenia'!$B$42</f>
-        <v/>
-      </c>
-      <c r="Q13" s="16">
-        <f>IF(A13&gt;='Zalozenia'!$B$67,'Zalozenia'!$B$68,0)</f>
-        <v/>
-      </c>
-      <c r="R13" s="16">
-        <f>M13-O13-P13-Q13</f>
-        <v/>
-      </c>
-      <c r="S13" s="16">
-        <f>S12+R13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="17">
-        <f>IF(A14&lt;=3,'Zalozenia'!$B$58,IF(A14&lt;=6,'Zalozenia'!$B$59,IF(A14&lt;=9,'Zalozenia'!$B$60,'Zalozenia'!$B$61)))</f>
-        <v/>
-      </c>
-      <c r="C14" s="25">
-        <f>'Zalozenia'!$B$51*B14</f>
-        <v/>
-      </c>
-      <c r="D14" s="25">
-        <f>F13*(1-'Zalozenia'!$B$62)</f>
-        <v/>
-      </c>
-      <c r="E14" s="25">
-        <f>IF(A14&lt;=3,MIN(C14,MAX(0,'Zalozenia'!$B$63-D14)),0)</f>
-        <v/>
-      </c>
-      <c r="F14" s="25">
-        <f>D14+E14</f>
-        <v/>
-      </c>
-      <c r="G14" s="25">
-        <f>I13*(1-'Zalozenia'!$B$62)</f>
-        <v/>
-      </c>
-      <c r="H14" s="25">
-        <f>C14-E14</f>
-        <v/>
-      </c>
-      <c r="I14" s="25">
-        <f>G14+H14</f>
-        <v/>
-      </c>
-      <c r="J14" s="25">
-        <f>F14+I14</f>
-        <v/>
-      </c>
-      <c r="K14" s="16">
-        <f>F14*'Zalozenia'!$B$31+I14*'Zalozenia'!$B$32</f>
-        <v/>
-      </c>
-      <c r="L14" s="16">
-        <f>H14*'Zalozenia'!$B$33</f>
-        <v/>
-      </c>
-      <c r="M14" s="16">
-        <f>K14+L14</f>
-        <v/>
-      </c>
-      <c r="N14" s="16">
-        <f>IF(A14&lt;=3,'Zalozenia'!$B$64,IF(A14&lt;=8,'Zalozenia'!$B$65,'Zalozenia'!$B$66))</f>
-        <v/>
-      </c>
-      <c r="O14" s="16">
-        <f>J14*N14</f>
-        <v/>
-      </c>
-      <c r="P14" s="16">
-        <f>'Zalozenia'!$B$41+'Zalozenia'!$B$42</f>
-        <v/>
-      </c>
-      <c r="Q14" s="16">
-        <f>IF(A14&gt;='Zalozenia'!$B$67,'Zalozenia'!$B$68,0)</f>
-        <v/>
-      </c>
-      <c r="R14" s="16">
-        <f>M14-O14-P14-Q14</f>
-        <v/>
-      </c>
-      <c r="S14" s="16">
-        <f>S13+R14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="17">
-        <f>IF(A15&lt;=3,'Zalozenia'!$B$58,IF(A15&lt;=6,'Zalozenia'!$B$59,IF(A15&lt;=9,'Zalozenia'!$B$60,'Zalozenia'!$B$61)))</f>
-        <v/>
-      </c>
-      <c r="C15" s="25">
-        <f>'Zalozenia'!$B$51*B15</f>
-        <v/>
-      </c>
-      <c r="D15" s="25">
-        <f>F14*(1-'Zalozenia'!$B$62)</f>
-        <v/>
-      </c>
-      <c r="E15" s="25">
-        <f>IF(A15&lt;=3,MIN(C15,MAX(0,'Zalozenia'!$B$63-D15)),0)</f>
-        <v/>
-      </c>
-      <c r="F15" s="25">
-        <f>D15+E15</f>
-        <v/>
-      </c>
-      <c r="G15" s="25">
-        <f>I14*(1-'Zalozenia'!$B$62)</f>
-        <v/>
-      </c>
-      <c r="H15" s="25">
-        <f>C15-E15</f>
-        <v/>
-      </c>
-      <c r="I15" s="25">
-        <f>G15+H15</f>
-        <v/>
-      </c>
-      <c r="J15" s="25">
-        <f>F15+I15</f>
-        <v/>
-      </c>
-      <c r="K15" s="16">
-        <f>F15*'Zalozenia'!$B$31+I15*'Zalozenia'!$B$32</f>
-        <v/>
-      </c>
-      <c r="L15" s="16">
-        <f>H15*'Zalozenia'!$B$33</f>
-        <v/>
-      </c>
-      <c r="M15" s="16">
-        <f>K15+L15</f>
-        <v/>
-      </c>
-      <c r="N15" s="16">
-        <f>IF(A15&lt;=3,'Zalozenia'!$B$64,IF(A15&lt;=8,'Zalozenia'!$B$65,'Zalozenia'!$B$66))</f>
-        <v/>
-      </c>
-      <c r="O15" s="16">
-        <f>J15*N15</f>
-        <v/>
-      </c>
-      <c r="P15" s="16">
-        <f>'Zalozenia'!$B$41+'Zalozenia'!$B$42</f>
-        <v/>
-      </c>
-      <c r="Q15" s="16">
-        <f>IF(A15&gt;='Zalozenia'!$B$67,'Zalozenia'!$B$68,0)</f>
-        <v/>
-      </c>
-      <c r="R15" s="16">
-        <f>M15-O15-P15-Q15</f>
-        <v/>
-      </c>
-      <c r="S15" s="16">
-        <f>S14+R15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="17">
-        <f>IF(A16&lt;=3,'Zalozenia'!$B$58,IF(A16&lt;=6,'Zalozenia'!$B$59,IF(A16&lt;=9,'Zalozenia'!$B$60,'Zalozenia'!$B$61)))</f>
-        <v/>
-      </c>
-      <c r="C16" s="25">
-        <f>'Zalozenia'!$B$51*B16</f>
-        <v/>
-      </c>
-      <c r="D16" s="25">
-        <f>F15*(1-'Zalozenia'!$B$62)</f>
-        <v/>
-      </c>
-      <c r="E16" s="25">
-        <f>IF(A16&lt;=3,MIN(C16,MAX(0,'Zalozenia'!$B$63-D16)),0)</f>
-        <v/>
-      </c>
-      <c r="F16" s="25">
-        <f>D16+E16</f>
-        <v/>
-      </c>
-      <c r="G16" s="25">
-        <f>I15*(1-'Zalozenia'!$B$62)</f>
-        <v/>
-      </c>
-      <c r="H16" s="25">
-        <f>C16-E16</f>
-        <v/>
-      </c>
-      <c r="I16" s="25">
-        <f>G16+H16</f>
-        <v/>
-      </c>
-      <c r="J16" s="25">
-        <f>F16+I16</f>
-        <v/>
-      </c>
-      <c r="K16" s="16">
-        <f>F16*'Zalozenia'!$B$31+I16*'Zalozenia'!$B$32</f>
-        <v/>
-      </c>
-      <c r="L16" s="16">
-        <f>H16*'Zalozenia'!$B$33</f>
-        <v/>
-      </c>
-      <c r="M16" s="16">
-        <f>K16+L16</f>
-        <v/>
-      </c>
-      <c r="N16" s="16">
-        <f>IF(A16&lt;=3,'Zalozenia'!$B$64,IF(A16&lt;=8,'Zalozenia'!$B$65,'Zalozenia'!$B$66))</f>
-        <v/>
-      </c>
-      <c r="O16" s="16">
-        <f>J16*N16</f>
-        <v/>
-      </c>
-      <c r="P16" s="16">
-        <f>'Zalozenia'!$B$41+'Zalozenia'!$B$42</f>
-        <v/>
-      </c>
-      <c r="Q16" s="16">
-        <f>IF(A16&gt;='Zalozenia'!$B$67,'Zalozenia'!$B$68,0)</f>
-        <v/>
-      </c>
-      <c r="R16" s="16">
-        <f>M16-O16-P16-Q16</f>
-        <v/>
-      </c>
-      <c r="S16" s="16">
-        <f>S15+R16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>Wynik narastajaco po wycenie pracy zalozycielow</t>
-        </is>
-      </c>
-      <c r="D18" s="26">
-        <f>S16-'Zalozenia'!$B$48*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Wynik narastajaco bez wynagrodzen to nie zysk, tylko zysk plus dwie nieoplacone pensje. Uzywaj liczby powyzej.</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3937,4 +3344,606 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Plan dwunastu miesiecy, model masowy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>PROGNOZA. Brak oplaty wdrozeniowej, caly przychod powtarzalny.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Mies.</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Konwersja</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Nowych</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Klientow</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>MRR</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>COGS</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Koszty stale</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>Wynik</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Narastajaco</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>Godziny Mario</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="17">
+        <f>IF(A5&lt;=3,'Zalozenia'!$B$93,IF(A5&lt;=6,'Zalozenia'!$B$94,IF(A5&lt;=9,'Zalozenia'!$B$95,'Zalozenia'!$B$96)))</f>
+        <v/>
+      </c>
+      <c r="C5" s="25">
+        <f>'Zalozenia'!$B$51*B5</f>
+        <v/>
+      </c>
+      <c r="D5" s="32">
+        <f>C5</f>
+        <v/>
+      </c>
+      <c r="E5" s="16">
+        <f>D5*Cennik!$B$26</f>
+        <v/>
+      </c>
+      <c r="F5" s="16">
+        <f>D5*Cennik!$B$27</f>
+        <v/>
+      </c>
+      <c r="G5" s="16">
+        <f>'Zalozenia'!$B$41+'Zalozenia'!$B$42</f>
+        <v/>
+      </c>
+      <c r="H5" s="16">
+        <f>E5-F5-G5</f>
+        <v/>
+      </c>
+      <c r="I5" s="16">
+        <f>H5</f>
+        <v/>
+      </c>
+      <c r="J5" s="35">
+        <f>40+'Zalozenia'!$B$51*1.5+C5*'Zalozenia'!$B$97+D5*'Zalozenia'!$B$98</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="17">
+        <f>IF(A6&lt;=3,'Zalozenia'!$B$93,IF(A6&lt;=6,'Zalozenia'!$B$94,IF(A6&lt;=9,'Zalozenia'!$B$95,'Zalozenia'!$B$96)))</f>
+        <v/>
+      </c>
+      <c r="C6" s="25">
+        <f>'Zalozenia'!$B$51*B6</f>
+        <v/>
+      </c>
+      <c r="D6" s="32">
+        <f>D5*(1-'Zalozenia'!$B$62)+C6</f>
+        <v/>
+      </c>
+      <c r="E6" s="16">
+        <f>D6*Cennik!$B$26</f>
+        <v/>
+      </c>
+      <c r="F6" s="16">
+        <f>D6*Cennik!$B$27</f>
+        <v/>
+      </c>
+      <c r="G6" s="16">
+        <f>'Zalozenia'!$B$41+'Zalozenia'!$B$42</f>
+        <v/>
+      </c>
+      <c r="H6" s="16">
+        <f>E6-F6-G6</f>
+        <v/>
+      </c>
+      <c r="I6" s="16">
+        <f>I5+H6</f>
+        <v/>
+      </c>
+      <c r="J6" s="35">
+        <f>40+'Zalozenia'!$B$51*1.5+C6*'Zalozenia'!$B$97+D6*'Zalozenia'!$B$98</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="17">
+        <f>IF(A7&lt;=3,'Zalozenia'!$B$93,IF(A7&lt;=6,'Zalozenia'!$B$94,IF(A7&lt;=9,'Zalozenia'!$B$95,'Zalozenia'!$B$96)))</f>
+        <v/>
+      </c>
+      <c r="C7" s="25">
+        <f>'Zalozenia'!$B$51*B7</f>
+        <v/>
+      </c>
+      <c r="D7" s="32">
+        <f>D6*(1-'Zalozenia'!$B$62)+C7</f>
+        <v/>
+      </c>
+      <c r="E7" s="16">
+        <f>D7*Cennik!$B$26</f>
+        <v/>
+      </c>
+      <c r="F7" s="16">
+        <f>D7*Cennik!$B$27</f>
+        <v/>
+      </c>
+      <c r="G7" s="16">
+        <f>'Zalozenia'!$B$41+'Zalozenia'!$B$42</f>
+        <v/>
+      </c>
+      <c r="H7" s="16">
+        <f>E7-F7-G7</f>
+        <v/>
+      </c>
+      <c r="I7" s="16">
+        <f>I6+H7</f>
+        <v/>
+      </c>
+      <c r="J7" s="35">
+        <f>40+'Zalozenia'!$B$51*1.5+C7*'Zalozenia'!$B$97+D7*'Zalozenia'!$B$98</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="17">
+        <f>IF(A8&lt;=3,'Zalozenia'!$B$93,IF(A8&lt;=6,'Zalozenia'!$B$94,IF(A8&lt;=9,'Zalozenia'!$B$95,'Zalozenia'!$B$96)))</f>
+        <v/>
+      </c>
+      <c r="C8" s="25">
+        <f>'Zalozenia'!$B$51*B8</f>
+        <v/>
+      </c>
+      <c r="D8" s="32">
+        <f>D7*(1-'Zalozenia'!$B$62)+C8</f>
+        <v/>
+      </c>
+      <c r="E8" s="16">
+        <f>D8*Cennik!$B$26</f>
+        <v/>
+      </c>
+      <c r="F8" s="16">
+        <f>D8*Cennik!$B$27</f>
+        <v/>
+      </c>
+      <c r="G8" s="16">
+        <f>'Zalozenia'!$B$41+'Zalozenia'!$B$42</f>
+        <v/>
+      </c>
+      <c r="H8" s="16">
+        <f>E8-F8-G8</f>
+        <v/>
+      </c>
+      <c r="I8" s="16">
+        <f>I7+H8</f>
+        <v/>
+      </c>
+      <c r="J8" s="35">
+        <f>40+'Zalozenia'!$B$51*1.5+C8*'Zalozenia'!$B$97+D8*'Zalozenia'!$B$98</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="17">
+        <f>IF(A9&lt;=3,'Zalozenia'!$B$93,IF(A9&lt;=6,'Zalozenia'!$B$94,IF(A9&lt;=9,'Zalozenia'!$B$95,'Zalozenia'!$B$96)))</f>
+        <v/>
+      </c>
+      <c r="C9" s="25">
+        <f>'Zalozenia'!$B$51*B9</f>
+        <v/>
+      </c>
+      <c r="D9" s="32">
+        <f>D8*(1-'Zalozenia'!$B$62)+C9</f>
+        <v/>
+      </c>
+      <c r="E9" s="16">
+        <f>D9*Cennik!$B$26</f>
+        <v/>
+      </c>
+      <c r="F9" s="16">
+        <f>D9*Cennik!$B$27</f>
+        <v/>
+      </c>
+      <c r="G9" s="16">
+        <f>'Zalozenia'!$B$41+'Zalozenia'!$B$42</f>
+        <v/>
+      </c>
+      <c r="H9" s="16">
+        <f>E9-F9-G9</f>
+        <v/>
+      </c>
+      <c r="I9" s="16">
+        <f>I8+H9</f>
+        <v/>
+      </c>
+      <c r="J9" s="35">
+        <f>40+'Zalozenia'!$B$51*1.5+C9*'Zalozenia'!$B$97+D9*'Zalozenia'!$B$98</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="17">
+        <f>IF(A10&lt;=3,'Zalozenia'!$B$93,IF(A10&lt;=6,'Zalozenia'!$B$94,IF(A10&lt;=9,'Zalozenia'!$B$95,'Zalozenia'!$B$96)))</f>
+        <v/>
+      </c>
+      <c r="C10" s="25">
+        <f>'Zalozenia'!$B$51*B10</f>
+        <v/>
+      </c>
+      <c r="D10" s="32">
+        <f>D9*(1-'Zalozenia'!$B$62)+C10</f>
+        <v/>
+      </c>
+      <c r="E10" s="16">
+        <f>D10*Cennik!$B$26</f>
+        <v/>
+      </c>
+      <c r="F10" s="16">
+        <f>D10*Cennik!$B$27</f>
+        <v/>
+      </c>
+      <c r="G10" s="16">
+        <f>'Zalozenia'!$B$41+'Zalozenia'!$B$42</f>
+        <v/>
+      </c>
+      <c r="H10" s="16">
+        <f>E10-F10-G10</f>
+        <v/>
+      </c>
+      <c r="I10" s="16">
+        <f>I9+H10</f>
+        <v/>
+      </c>
+      <c r="J10" s="35">
+        <f>40+'Zalozenia'!$B$51*1.5+C10*'Zalozenia'!$B$97+D10*'Zalozenia'!$B$98</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="17">
+        <f>IF(A11&lt;=3,'Zalozenia'!$B$93,IF(A11&lt;=6,'Zalozenia'!$B$94,IF(A11&lt;=9,'Zalozenia'!$B$95,'Zalozenia'!$B$96)))</f>
+        <v/>
+      </c>
+      <c r="C11" s="25">
+        <f>'Zalozenia'!$B$51*B11</f>
+        <v/>
+      </c>
+      <c r="D11" s="32">
+        <f>D10*(1-'Zalozenia'!$B$62)+C11</f>
+        <v/>
+      </c>
+      <c r="E11" s="16">
+        <f>D11*Cennik!$B$26</f>
+        <v/>
+      </c>
+      <c r="F11" s="16">
+        <f>D11*Cennik!$B$27</f>
+        <v/>
+      </c>
+      <c r="G11" s="16">
+        <f>'Zalozenia'!$B$41+'Zalozenia'!$B$42</f>
+        <v/>
+      </c>
+      <c r="H11" s="16">
+        <f>E11-F11-G11</f>
+        <v/>
+      </c>
+      <c r="I11" s="16">
+        <f>I10+H11</f>
+        <v/>
+      </c>
+      <c r="J11" s="35">
+        <f>40+'Zalozenia'!$B$51*1.5+C11*'Zalozenia'!$B$97+D11*'Zalozenia'!$B$98</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="17">
+        <f>IF(A12&lt;=3,'Zalozenia'!$B$93,IF(A12&lt;=6,'Zalozenia'!$B$94,IF(A12&lt;=9,'Zalozenia'!$B$95,'Zalozenia'!$B$96)))</f>
+        <v/>
+      </c>
+      <c r="C12" s="25">
+        <f>'Zalozenia'!$B$51*B12</f>
+        <v/>
+      </c>
+      <c r="D12" s="32">
+        <f>D11*(1-'Zalozenia'!$B$62)+C12</f>
+        <v/>
+      </c>
+      <c r="E12" s="16">
+        <f>D12*Cennik!$B$26</f>
+        <v/>
+      </c>
+      <c r="F12" s="16">
+        <f>D12*Cennik!$B$27</f>
+        <v/>
+      </c>
+      <c r="G12" s="16">
+        <f>'Zalozenia'!$B$41+'Zalozenia'!$B$42</f>
+        <v/>
+      </c>
+      <c r="H12" s="16">
+        <f>E12-F12-G12</f>
+        <v/>
+      </c>
+      <c r="I12" s="16">
+        <f>I11+H12</f>
+        <v/>
+      </c>
+      <c r="J12" s="35">
+        <f>40+'Zalozenia'!$B$51*1.5+C12*'Zalozenia'!$B$97+D12*'Zalozenia'!$B$98</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="17">
+        <f>IF(A13&lt;=3,'Zalozenia'!$B$93,IF(A13&lt;=6,'Zalozenia'!$B$94,IF(A13&lt;=9,'Zalozenia'!$B$95,'Zalozenia'!$B$96)))</f>
+        <v/>
+      </c>
+      <c r="C13" s="25">
+        <f>'Zalozenia'!$B$51*B13</f>
+        <v/>
+      </c>
+      <c r="D13" s="32">
+        <f>D12*(1-'Zalozenia'!$B$62)+C13</f>
+        <v/>
+      </c>
+      <c r="E13" s="16">
+        <f>D13*Cennik!$B$26</f>
+        <v/>
+      </c>
+      <c r="F13" s="16">
+        <f>D13*Cennik!$B$27</f>
+        <v/>
+      </c>
+      <c r="G13" s="16">
+        <f>'Zalozenia'!$B$41+'Zalozenia'!$B$42</f>
+        <v/>
+      </c>
+      <c r="H13" s="16">
+        <f>E13-F13-G13</f>
+        <v/>
+      </c>
+      <c r="I13" s="16">
+        <f>I12+H13</f>
+        <v/>
+      </c>
+      <c r="J13" s="35">
+        <f>40+'Zalozenia'!$B$51*1.5+C13*'Zalozenia'!$B$97+D13*'Zalozenia'!$B$98</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="17">
+        <f>IF(A14&lt;=3,'Zalozenia'!$B$93,IF(A14&lt;=6,'Zalozenia'!$B$94,IF(A14&lt;=9,'Zalozenia'!$B$95,'Zalozenia'!$B$96)))</f>
+        <v/>
+      </c>
+      <c r="C14" s="25">
+        <f>'Zalozenia'!$B$51*B14</f>
+        <v/>
+      </c>
+      <c r="D14" s="32">
+        <f>D13*(1-'Zalozenia'!$B$62)+C14</f>
+        <v/>
+      </c>
+      <c r="E14" s="16">
+        <f>D14*Cennik!$B$26</f>
+        <v/>
+      </c>
+      <c r="F14" s="16">
+        <f>D14*Cennik!$B$27</f>
+        <v/>
+      </c>
+      <c r="G14" s="16">
+        <f>'Zalozenia'!$B$41+'Zalozenia'!$B$42</f>
+        <v/>
+      </c>
+      <c r="H14" s="16">
+        <f>E14-F14-G14</f>
+        <v/>
+      </c>
+      <c r="I14" s="16">
+        <f>I13+H14</f>
+        <v/>
+      </c>
+      <c r="J14" s="35">
+        <f>40+'Zalozenia'!$B$51*1.5+C14*'Zalozenia'!$B$97+D14*'Zalozenia'!$B$98</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="17">
+        <f>IF(A15&lt;=3,'Zalozenia'!$B$93,IF(A15&lt;=6,'Zalozenia'!$B$94,IF(A15&lt;=9,'Zalozenia'!$B$95,'Zalozenia'!$B$96)))</f>
+        <v/>
+      </c>
+      <c r="C15" s="25">
+        <f>'Zalozenia'!$B$51*B15</f>
+        <v/>
+      </c>
+      <c r="D15" s="32">
+        <f>D14*(1-'Zalozenia'!$B$62)+C15</f>
+        <v/>
+      </c>
+      <c r="E15" s="16">
+        <f>D15*Cennik!$B$26</f>
+        <v/>
+      </c>
+      <c r="F15" s="16">
+        <f>D15*Cennik!$B$27</f>
+        <v/>
+      </c>
+      <c r="G15" s="16">
+        <f>'Zalozenia'!$B$41+'Zalozenia'!$B$42</f>
+        <v/>
+      </c>
+      <c r="H15" s="16">
+        <f>E15-F15-G15</f>
+        <v/>
+      </c>
+      <c r="I15" s="16">
+        <f>I14+H15</f>
+        <v/>
+      </c>
+      <c r="J15" s="35">
+        <f>40+'Zalozenia'!$B$51*1.5+C15*'Zalozenia'!$B$97+D15*'Zalozenia'!$B$98</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="17">
+        <f>IF(A16&lt;=3,'Zalozenia'!$B$93,IF(A16&lt;=6,'Zalozenia'!$B$94,IF(A16&lt;=9,'Zalozenia'!$B$95,'Zalozenia'!$B$96)))</f>
+        <v/>
+      </c>
+      <c r="C16" s="25">
+        <f>'Zalozenia'!$B$51*B16</f>
+        <v/>
+      </c>
+      <c r="D16" s="32">
+        <f>D15*(1-'Zalozenia'!$B$62)+C16</f>
+        <v/>
+      </c>
+      <c r="E16" s="16">
+        <f>D16*Cennik!$B$26</f>
+        <v/>
+      </c>
+      <c r="F16" s="16">
+        <f>D16*Cennik!$B$27</f>
+        <v/>
+      </c>
+      <c r="G16" s="16">
+        <f>'Zalozenia'!$B$41+'Zalozenia'!$B$42</f>
+        <v/>
+      </c>
+      <c r="H16" s="16">
+        <f>E16-F16-G16</f>
+        <v/>
+      </c>
+      <c r="I16" s="16">
+        <f>I15+H16</f>
+        <v/>
+      </c>
+      <c r="J16" s="35">
+        <f>40+'Zalozenia'!$B$51*1.5+C16*'Zalozenia'!$B$97+D16*'Zalozenia'!$B$98</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Wynik narastajaco po wycenie pracy obu zalozycieli</t>
+        </is>
+      </c>
+      <c r="D18" s="26">
+        <f>I16-'Zalozenia'!$B$48*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Kolumna Godziny Mario: outbound 40 h + spotkania + onboarding + wsparcie. Powyzej ~170 h potrzebna pierwsza osoba.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/analysis/model-valenos.xlsx
+++ b/analysis/model-valenos.xlsx
@@ -85,7 +85,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -98,11 +98,12 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -142,6 +143,18 @@
     <xf numFmtId="165" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2812,7 +2825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -2822,215 +2835,284 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Wykorzystanie srodkow z rundy</t>
-        </is>
-      </c>
+      <c r="A1" s="37" t="inlineStr">
+        <is>
+          <t>Wykorzystanie srodkow z rundy (liczby od Mario)</t>
+        </is>
+      </c>
+      <c r="B1" s="38" t="n"/>
+      <c r="C1" s="38" t="n"/>
+      <c r="D1" s="38" t="n"/>
+      <c r="E1" s="38" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="39" t="inlineStr">
+        <is>
+          <t>Okres: szesc miesiecy. Zalozyciele nie pobieraja wynagrodzenia z rundy.</t>
+        </is>
+      </c>
+      <c r="B2" s="38" t="n"/>
+      <c r="C2" s="38" t="n"/>
+      <c r="D2" s="38" t="n"/>
+      <c r="E2" s="38" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="40" t="n"/>
+      <c r="B3" s="40" t="n"/>
+      <c r="C3" s="40" t="n"/>
+      <c r="D3" s="40" t="n"/>
+      <c r="E3" s="38" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="41" t="inlineStr">
+        <is>
+          <t>Claude Max 20x: liczba subskrypcji</t>
+        </is>
+      </c>
+      <c r="B4" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" s="43" t="n"/>
+      <c r="D4" s="41" t="n"/>
+      <c r="E4" s="38" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="41" t="inlineStr">
+        <is>
+          <t>Claude Max 20x: cena miesieczna (USD)</t>
+        </is>
+      </c>
+      <c r="B5" s="42" t="n">
+        <v>200</v>
+      </c>
+      <c r="C5" s="43" t="n"/>
+      <c r="D5" s="41" t="n"/>
+      <c r="E5" s="38" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="41" t="inlineStr">
+        <is>
+          <t>Okres (miesiecy)</t>
+        </is>
+      </c>
+      <c r="B6" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" s="43" t="n"/>
+      <c r="D6" s="41" t="n"/>
+      <c r="E6" s="38" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="41" t="n"/>
+      <c r="B7" s="44" t="n"/>
+      <c r="C7" s="43" t="n"/>
+      <c r="D7" s="41" t="n"/>
+      <c r="E7" s="38" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Pozycja</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>Kwota</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
         <is>
           <t>Udzial</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Budowa?</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Agenty i warstwa kontekstu: inferencja modelowa</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="n">
-        <v>19000</v>
-      </c>
-      <c r="C4" s="17">
-        <f>B4/$B$12</f>
-        <v/>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E8" s="38" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="41" t="inlineStr">
+        <is>
+          <t>Claude Max 20x, cztery subskrypcje, szesc miesiecy</t>
+        </is>
+      </c>
+      <c r="B9" s="45">
+        <f>B4*B5*B6*'Zalozenia'!$B$3</f>
+        <v/>
+      </c>
+      <c r="C9" s="43">
+        <f>B9/$B$15</f>
+        <v/>
+      </c>
+      <c r="D9" s="41" t="inlineStr">
         <is>
           <t>tak</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Agenty i kontekst: kredyty Apollo i wyszukiwanie</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="n">
-        <v>3500</v>
-      </c>
-      <c r="C5" s="17">
-        <f>B5/$B$12</f>
-        <v/>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="E9" s="38" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="41" t="inlineStr">
+        <is>
+          <t>Narzedzia i API: Apollo, wyszukiwarka, wysylka, hosting</t>
+        </is>
+      </c>
+      <c r="B10" s="42" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C10" s="43">
+        <f>B10/$B$15</f>
+        <v/>
+      </c>
+      <c r="D10" s="41" t="inlineStr">
         <is>
           <t>tak</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Infrastruktura platformy, 6 miesiecy</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="n">
-        <v>4600</v>
-      </c>
-      <c r="C6" s="17">
-        <f>B6/$B$12</f>
-        <v/>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>tak</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Design produktu</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="n">
+      <c r="E10" s="38" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="41" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="B11" s="42" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C11" s="43">
+        <f>B11/$B$15</f>
+        <v/>
+      </c>
+      <c r="D11" s="41" t="inlineStr">
+        <is>
+          <t>nie</t>
+        </is>
+      </c>
+      <c r="E11" s="38" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="41" t="inlineStr">
+        <is>
+          <t>Ksiegowosc i operacje</t>
+        </is>
+      </c>
+      <c r="B12" s="42" t="n">
         <v>5000</v>
       </c>
-      <c r="C7" s="17">
-        <f>B7/$B$12</f>
-        <v/>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>tak</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Sprzedaz: wlasny stack outboundowy, 6 miesiecy</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="n">
-        <v>12000</v>
-      </c>
-      <c r="C8" s="17">
-        <f>B8/$B$12</f>
-        <v/>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="C12" s="46">
+        <f>B12/$B$15</f>
+        <v/>
+      </c>
+      <c r="D12" s="41" t="inlineStr">
         <is>
           <t>nie</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Operacje: ksiegowosc, narzedzia, dokumenty dla klientow</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="n">
-        <v>4400</v>
-      </c>
-      <c r="C9" s="17">
-        <f>B9/$B$12</f>
-        <v/>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="E12" s="38" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="38" t="inlineStr">
+        <is>
+          <t>Rezerwa</t>
+        </is>
+      </c>
+      <c r="B13" s="45">
+        <f>50000-SUM(B9:B12)</f>
+        <v/>
+      </c>
+      <c r="C13" s="43">
+        <f>B13/$B$15</f>
+        <v/>
+      </c>
+      <c r="D13" s="38" t="inlineStr">
         <is>
           <t>nie</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Rezerwa</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="n">
-        <v>1500</v>
-      </c>
-      <c r="C10" s="17">
-        <f>B10/$B$12</f>
-        <v/>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>nie</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="E13" s="38" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="40" t="n"/>
+      <c r="B14" s="47" t="n"/>
+      <c r="C14" s="46" t="n"/>
+      <c r="D14" s="38" t="n"/>
+      <c r="E14" s="38" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Razem</t>
         </is>
       </c>
-      <c r="B12" s="15">
-        <f>SUM(B4:B10)</f>
-        <v/>
-      </c>
-      <c r="C12" s="30">
-        <f>SUM(C4:C10)</f>
-        <v/>
-      </c>
-      <c r="D12" s="6" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>Udzial na budowe oprogramowania</t>
-        </is>
-      </c>
-      <c r="B14" s="26">
-        <f>SUMIF(D4:D10,"tak",B4:B10)</f>
-        <v/>
-      </c>
-      <c r="C14" s="31">
-        <f>B14/B12</f>
-        <v/>
-      </c>
+      <c r="B15" s="15">
+        <f>SUM(B9:B13)</f>
+        <v/>
+      </c>
+      <c r="C15" s="30">
+        <f>SUM(C9:C13)</f>
+        <v/>
+      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="38" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Miesiecy pasa startowego z samych kosztow stalych</t>
-        </is>
-      </c>
-      <c r="B16" s="32">
-        <f>B12/('Zalozenia'!$B$41+'Zalozenia'!$B$42)</f>
-        <v/>
-      </c>
+      <c r="A16" s="38" t="n"/>
+      <c r="B16" s="48" t="n"/>
+      <c r="C16" s="38" t="n"/>
+      <c r="D16" s="38" t="n"/>
+      <c r="E16" s="38" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="40" t="inlineStr">
+        <is>
+          <t>Udzial na budowe produktu</t>
+        </is>
+      </c>
+      <c r="B17" s="47">
+        <f>SUMIF(D9:D13,"tak",B9:B13)</f>
+        <v/>
+      </c>
+      <c r="C17" s="46">
+        <f>B17/B15</f>
+        <v/>
+      </c>
+      <c r="D17" s="38" t="n"/>
+      <c r="E17" s="38" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Najwieksze ryzyko: inferencja w fazie strojenia agentow. Przy dwukrotnosci zakladanej liczby iteracji sam koszt modelu pochlania runde.</t>
-        </is>
-      </c>
+      <c r="A18" s="39" t="n"/>
+      <c r="B18" s="38" t="n"/>
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="38" t="n"/>
+      <c r="E18" s="38" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="39" t="inlineStr">
+        <is>
+          <t>Subskrypcje Claude Max pokrywaja prace zespolu nad produktem. Inferencja agentow u klientow to osobny koszt rozliczany per token, ktory jest kosztem przychodu i pokrywa go przychod, a nie runda.</t>
+        </is>
+      </c>
+      <c r="B19" s="38" t="n"/>
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="38" t="n"/>
+      <c r="E19" s="38" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="38" t="n"/>
+      <c r="B20" s="38" t="n"/>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="38" t="n"/>
+      <c r="E20" s="38" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="38" t="n"/>
+      <c r="B21" s="38" t="n"/>
+      <c r="C21" s="38" t="n"/>
+      <c r="D21" s="38" t="n"/>
+      <c r="E21" s="38" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
